--- a/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,41</t>
+          <t>-2,26; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,54</t>
+          <t>-1,91; 2,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 12,86</t>
+          <t>2,2; 13,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,82</t>
+          <t>1,45; 7,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,1</t>
+          <t>2,54; 10,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,76</t>
+          <t>0,26; 3,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,26</t>
+          <t>-0,45; 2,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,67</t>
+          <t>3,2; 9,69</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,92; —</t>
+          <t>-27,1; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,73; —</t>
+          <t>-60,11; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120,58; —</t>
+          <t>74,18; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,13</t>
+          <t>-2,34; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,19</t>
+          <t>-2,86; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 7,12</t>
+          <t>-0,63; 7,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,45</t>
+          <t>-3,3; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,43</t>
+          <t>-2,22; 4,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,58</t>
+          <t>-0,92; 7,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,84</t>
+          <t>-1,91; 2,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,27</t>
+          <t>-1,19; 3,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,96</t>
+          <t>0,53; 6,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 121,12</t>
+          <t>-41,69; 132,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 132,48</t>
+          <t>-47,75; 124,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 228,82</t>
+          <t>-15,38; 219,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 93,53</t>
+          <t>-49,2; 80,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 120,94</t>
+          <t>-35,61; 105,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 215,54</t>
+          <t>-19,49; 184,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 72,51</t>
+          <t>-31,25; 71,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 84,37</t>
+          <t>-20,19; 87,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 151,44</t>
+          <t>7,57; 154,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,79</t>
+          <t>-6,24; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 6,98</t>
+          <t>-5,29; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 4,14</t>
+          <t>-8,64; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 9,45</t>
+          <t>-1,97; 8,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 8,14</t>
+          <t>-2,3; 8,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 12,55</t>
+          <t>0,87; 13,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,01</t>
+          <t>-2,54; 6,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,37</t>
+          <t>-2,15; 5,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,82</t>
+          <t>-1,63; 6,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 68,09</t>
+          <t>-41,15; 67,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 78,86</t>
+          <t>-32,66; 84,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,28; 51,07</t>
+          <t>-52,96; 38,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 152,65</t>
+          <t>-18,88; 146,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 128,58</t>
+          <t>-21,66; 150,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 213,02</t>
+          <t>3,71; 214,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 72,77</t>
+          <t>-20,09; 75,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 75,18</t>
+          <t>-18,25; 71,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 79,72</t>
+          <t>-14,36; 80,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 4,38</t>
+          <t>-10,17; 4,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,32; -3,65</t>
+          <t>-16,75; -3,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,69; -11,3</t>
+          <t>-23,07; -11,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 11,37</t>
+          <t>-3,26; 10,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 3,1</t>
+          <t>-10,59; 2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -5,2</t>
+          <t>-15,27; -4,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,19</t>
+          <t>-4,41; 5,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -2,29</t>
+          <t>-11,6; -1,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -8,87</t>
+          <t>-17,69; -9,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 20,13</t>
+          <t>-33,92; 22,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,2; -14,42</t>
+          <t>-56,96; -16,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,75; -49,74</t>
+          <t>-78,76; -49,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 61,52</t>
+          <t>-14,26; 59,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 18,51</t>
+          <t>-43,9; 14,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,21; -28,61</t>
+          <t>-65,68; -24,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 24,15</t>
+          <t>-17,46; 27,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -10,9</t>
+          <t>-46,07; -8,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,53; -43,54</t>
+          <t>-69,03; -45,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,46</t>
+          <t>-3,89; 1,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,3</t>
+          <t>-5,03; 0,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,12</t>
+          <t>-5,42; 0,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,03</t>
+          <t>-0,95; 4,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,26</t>
+          <t>-2,63; 2,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,22</t>
+          <t>-1,55; 4,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,11</t>
+          <t>-1,71; 2,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,66</t>
+          <t>-2,89; 0,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,4</t>
+          <t>-2,42; 1,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 14,37</t>
+          <t>-29,57; 13,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 3,48</t>
+          <t>-38,31; 3,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 1,04</t>
+          <t>-40,96; 1,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 47,33</t>
+          <t>-9,37; 48,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 27,52</t>
+          <t>-24,73; 26,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 49,2</t>
+          <t>-14,46; 47,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 21,92</t>
+          <t>-15,15; 22,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 7,18</t>
+          <t>-25,35; 7,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 14,29</t>
+          <t>-21,33; 16,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,46</t>
+          <t>-2,22; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,98</t>
+          <t>-2,01; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 13,34</t>
+          <t>2,13; 13,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,03</t>
+          <t>1,38; 6,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,91</t>
+          <t>2,81; 11,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,61</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,35</t>
+          <t>-0,5; 2,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,69</t>
+          <t>3,2; 9,89</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,1; —</t>
+          <t>-14,17; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,11; —</t>
+          <t>-31,98; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,18; —</t>
+          <t>89,87; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,05</t>
+          <t>-2,4; 4,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,22</t>
+          <t>-2,16; 4,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,37</t>
+          <t>-0,79; 7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,82</t>
+          <t>-3,11; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,08</t>
+          <t>-2,3; 4,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 7,0</t>
+          <t>-0,55; 7,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,71</t>
+          <t>-1,66; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,56</t>
+          <t>-1,14; 3,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,35</t>
+          <t>0,47; 5,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 132,09</t>
+          <t>-40,26; 131,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,75; 124,36</t>
+          <t>-38,7; 146,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 219,48</t>
+          <t>-16,72; 206,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 80,66</t>
+          <t>-45,44; 87,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 105,92</t>
+          <t>-37,57; 113,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 184,67</t>
+          <t>-12,42; 192,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 71,14</t>
+          <t>-28,17; 75,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 87,12</t>
+          <t>-19,85; 88,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 154,89</t>
+          <t>8,66; 157,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,06</t>
+          <t>-6,68; 5,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,01</t>
+          <t>-6,11; 6,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 3,21</t>
+          <t>-7,45; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 8,81</t>
+          <t>-2,85; 8,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,94</t>
+          <t>-2,08; 8,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 13,02</t>
+          <t>0,15; 12,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,34</t>
+          <t>-2,91; 5,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,97</t>
+          <t>-2,07; 5,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,83</t>
+          <t>-1,69; 6,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 67,43</t>
+          <t>-43,27; 67,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 84,37</t>
+          <t>-38,56; 74,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 38,46</t>
+          <t>-47,63; 61,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 146,62</t>
+          <t>-25,2; 142,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 150,04</t>
+          <t>-17,11; 162,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 214,97</t>
+          <t>-0,52; 196,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 75,94</t>
+          <t>-24,12; 65,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 71,92</t>
+          <t>-18,14; 74,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 80,65</t>
+          <t>-13,09; 84,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 4,74</t>
+          <t>-9,58; 5,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -3,98</t>
+          <t>-17,26; -3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,07; -11,2</t>
+          <t>-23,13; -10,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 10,23</t>
+          <t>-3,6; 10,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,51</t>
+          <t>-10,04; 2,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -4,38</t>
+          <t>-16,16; -4,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 5,66</t>
+          <t>-4,09; 5,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -1,82</t>
+          <t>-11,9; -2,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -9,64</t>
+          <t>-17,46; -9,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 22,05</t>
+          <t>-33,36; 22,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,96; -16,96</t>
+          <t>-57,72; -14,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,76; -49,57</t>
+          <t>-78,07; -47,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 59,97</t>
+          <t>-15,56; 63,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 14,88</t>
+          <t>-44,08; 16,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,68; -24,86</t>
+          <t>-66,47; -26,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 27,38</t>
+          <t>-16,09; 27,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,07; -8,47</t>
+          <t>-46,39; -9,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,03; -45,04</t>
+          <t>-68,1; -43,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,39</t>
+          <t>-3,71; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,35</t>
+          <t>-5,14; 0,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,13</t>
+          <t>-5,2; 0,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,03</t>
+          <t>-1,0; 4,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,27</t>
+          <t>-2,79; 2,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,02</t>
+          <t>-1,51; 4,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,16</t>
+          <t>-1,65; 2,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,72</t>
+          <t>-3,1; 0,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,6</t>
+          <t>-2,43; 1,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 13,56</t>
+          <t>-29,2; 15,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 3,7</t>
+          <t>-39,1; 4,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 1,95</t>
+          <t>-41,57; 2,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 48,77</t>
+          <t>-9,46; 54,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 26,08</t>
+          <t>-25,32; 30,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 47,72</t>
+          <t>-14,51; 50,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 22,32</t>
+          <t>-14,4; 21,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 7,38</t>
+          <t>-26,79; 6,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 16,89</t>
+          <t>-21,09; 16,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,54</t>
+          <t>1,46; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,05</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 13,31</t>
+          <t>2,16; 8,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,11</t>
+          <t>-2,4; 2,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>-1,63; 3,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,06</t>
+          <t>1,68; 12,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,67</t>
+          <t>0,27; 3,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,44</t>
+          <t>-0,41; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,89</t>
+          <t>2,67; 9,09</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>22,85%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>59,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>557,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>511,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1087,82%</t>
+          <t>984,14%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,17; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,7; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,98; —</t>
+          <t>-25,73; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,87; —</t>
+          <t>94,71; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>3,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,07</t>
+          <t>-2,77; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,5</t>
+          <t>-2,26; 4,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,35</t>
+          <t>-0,3; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,15</t>
+          <t>-2,13; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,39</t>
+          <t>-2,14; 4,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,34</t>
+          <t>0,15; 8,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,82</t>
+          <t>-1,74; 2,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,43</t>
+          <t>-1,37; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,97</t>
+          <t>0,7; 6,57</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>21,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>68,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 131,11</t>
+          <t>-43,47; 93,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 146,99</t>
+          <t>-35,78; 120,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 206,24</t>
+          <t>-6,57; 220,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 87,56</t>
+          <t>-37,88; 121,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 113,87</t>
+          <t>-39,23; 132,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 192,39</t>
+          <t>-1,5; 260,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 75,57</t>
+          <t>-30,29; 72,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 88,29</t>
+          <t>-22,95; 84,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 157,33</t>
+          <t>10,85; 166,15</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 5,74</t>
+          <t>-2,01; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 6,33</t>
+          <t>-2,55; 8,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 4,53</t>
+          <t>1,07; 13,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 8,82</t>
+          <t>-6,46; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 8,85</t>
+          <t>-5,42; 6,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,35</t>
+          <t>-7,64; 4,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,64</t>
+          <t>-2,5; 6,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,98</t>
+          <t>-2,14; 6,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,91</t>
+          <t>-1,45; 7,03</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,18%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-14,74%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>-14,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 67,02</t>
+          <t>-18,3; 152,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 74,61</t>
+          <t>-20,92; 128,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 61,56</t>
+          <t>7,48; 230,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 142,37</t>
+          <t>-42,77; 68,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 162,77</t>
+          <t>-33,55; 78,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 196,7</t>
+          <t>-50,35; 50,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 65,77</t>
+          <t>-20,12; 72,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 74,07</t>
+          <t>-16,95; 75,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 84,72</t>
+          <t>-12,38; 83,53</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,76</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-9,74</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-10,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-16,91</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,76</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,19</t>
+          <t>-15,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,45</t>
+          <t>-12,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 5,04</t>
+          <t>-3,14; 11,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -3,56</t>
+          <t>-9,71; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -10,87</t>
+          <t>-15,66; -4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 10,75</t>
+          <t>-10,17; 4,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 2,74</t>
+          <t>-17,32; -3,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -4,87</t>
+          <t>-22,21; -9,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,81</t>
+          <t>-5,0; 5,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -2,16</t>
+          <t>-12,18; -2,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,46; -9,21</t>
+          <t>-16,71; -8,26</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-18,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-47,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-10,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-40,31%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-64,89%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,19%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-49,36%</t>
+          <t>-60,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,75%</t>
+          <t>-54,18%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 22,94</t>
+          <t>-15,2; 61,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,72; -14,05</t>
+          <t>-40,63; 18,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,07; -47,92</t>
+          <t>-65,53; -25,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 63,15</t>
+          <t>-35,45; 20,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 16,11</t>
+          <t>-58,2; -14,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -26,46</t>
+          <t>-74,18; -43,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 27,81</t>
+          <t>-18,72; 24,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,39; -9,13</t>
+          <t>-46,65; -10,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,1; -43,51</t>
+          <t>-65,11; -39,75</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,52</t>
+          <t>-0,86; 4,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,45</t>
+          <t>-2,58; 2,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,31</t>
+          <t>-0,96; 4,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,33</t>
+          <t>-3,92; 1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,5</t>
+          <t>-4,95; 0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,2</t>
+          <t>-4,38; 0,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,05</t>
+          <t>-1,77; 2,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,6</t>
+          <t>-3,12; 0,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,61</t>
+          <t>-1,78; 2,0</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,47%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-10,45%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-19,08%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-22,62%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,47%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>-16,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 15,52</t>
+          <t>-9,16; 47,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 4,48</t>
+          <t>-25,15; 27,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 2,82</t>
+          <t>-8,54; 55,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 54,61</t>
+          <t>-30,1; 14,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 30,91</t>
+          <t>-38,25; 3,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 50,73</t>
+          <t>-34,64; 9,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 21,31</t>
+          <t>-15,13; 21,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 6,39</t>
+          <t>-26,87; 7,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 16,77</t>
+          <t>-15,68; 20,62</t>
         </is>
       </c>
     </row>
